--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -983,8 +983,10 @@
           <t>Q1 2026 Earnings 15.04.</t>
         </is>
       </c>
-      <c r="Q7" s="37" t="n">
-        <v>46129</v>
+      <c r="Q7" s="37" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R7" s="5" t="n">
         <v>0</v>
@@ -1069,8 +1071,10 @@
           <t>Q3 FY26 Earnings Jun 2026</t>
         </is>
       </c>
-      <c r="Q8" s="38" t="n">
-        <v>46129</v>
+      <c r="Q8" s="38" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R8" s="11" t="n">
         <v>0</v>
@@ -1155,8 +1159,10 @@
           <t>29.04.2026 Q3 FY26 Earnings</t>
         </is>
       </c>
-      <c r="Q9" s="37" t="n">
-        <v>46129</v>
+      <c r="Q9" s="37" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R9" s="5" t="n">
         <v>0</v>
@@ -1241,8 +1247,10 @@
           <t>28.05.2026</t>
         </is>
       </c>
-      <c r="Q10" s="38" t="n">
-        <v>46129</v>
+      <c r="Q10" s="38" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R10" s="11" t="n">
         <v>0</v>
@@ -1327,8 +1335,10 @@
           <t>H1 2026 Report Juli/Aug 2026</t>
         </is>
       </c>
-      <c r="Q11" s="37" t="n">
-        <v>46129</v>
+      <c r="Q11" s="37" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R11" s="5" t="n">
         <v>0</v>
@@ -1413,8 +1423,10 @@
           <t>21.05.2026 Q1 FY27</t>
         </is>
       </c>
-      <c r="Q12" s="38" t="n">
-        <v>46129</v>
+      <c r="Q12" s="38" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R12" s="11" t="n">
         <v>0</v>
@@ -1499,8 +1511,10 @@
           <t>07.05.2026</t>
         </is>
       </c>
-      <c r="Q13" s="37" t="n">
-        <v>46129</v>
+      <c r="Q13" s="37" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R13" s="5" t="n">
         <v>0</v>
@@ -1585,8 +1599,10 @@
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="Q14" s="38" t="n">
-        <v>46129</v>
+      <c r="Q14" s="38" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R14" s="11" t="n">
         <v>0</v>
@@ -1671,8 +1687,10 @@
           <t>22.07.2026</t>
         </is>
       </c>
-      <c r="Q15" s="37" t="n">
-        <v>46129</v>
+      <c r="Q15" s="37" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R15" s="5" t="n">
         <v>0</v>
@@ -1757,8 +1775,10 @@
           <t>23.04.2026 Q1 Earnings</t>
         </is>
       </c>
-      <c r="Q16" s="38" t="n">
-        <v>46129</v>
+      <c r="Q16" s="38" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R16" s="11" t="n">
         <v>0</v>
@@ -1843,8 +1863,10 @@
           <t>Q2 2025 Earnings 23.07.2025</t>
         </is>
       </c>
-      <c r="Q17" s="37" t="n">
-        <v>46129</v>
+      <c r="Q17" s="37" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
       </c>
       <c r="R17" s="5" t="n">
         <v>0</v>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -993,7 +993,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>[V] DEFCON 3 (68/100). Moat 19/20 Wide Monopol, Fwd P/E 38x + P/FCF ~41x = Bewertungsprämie ohne Sicherheitsmarge. China-Revenue 14.7% → Kein Tariff-FLAG.</t>
+          <t>[V] DEFCON 3 (68/100). Moat 19/20 Wide Monopol, Fwd P/E 38x + P/FCF ~41x = Bewertungsprämie ohne Sicherheitsmarge. China-Revenue 14.7% → Kein Tariff-FLAG.  |  [LV 17.04.] v3.7 Live-Verify: Score 66 ±2 bestätigt (OpM 36,1% / Fwd P/E 39,52 + P/FCF 48x → beide Fix-1-Zweige hart 0). WATCH: Fwd P/E FY27 30,30 Grenzfall — bei &lt;30 nach Guidance Score +1-2 (D4-Upside).</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>[V] Re-Analyse 15.04.2026: Score 71→69 (−2). Q1 2026: €4.07B (+6% CER, −1% reported). Miss vs. +7–8% Konsens. Kursreaktion −8.4% (€1.783→€1.632,50). 52W-Tief €1.529 intraday. Treiber: Mittlerer Osten −6% (Iran-Krieg, UAE Malls −40%), FX-Headwind €290M, China +2%. Positiv: Leder +9%, ROIC 24%&gt;&gt;WACC 6.5%, Insider Buy +€7.67M (AMF). Kein FLAG. Sparplan voll aktiv. Nächster Check: H1 2026 Report.</t>
+          <t>[V] Re-Analyse 15.04.2026: Score 71→69 (−2). Q1 2026: €4.07B (+6% CER, −1% reported). Miss vs. +7–8% Konsens. Kursreaktion −8.4% (€1.783→€1.632,50). 52W-Tief €1.529 intraday. Treiber: Mittlerer Osten −6% (Iran-Krieg, UAE Malls −40%), FX-Headwind €290M, China +2%. Positiv: Leder +9%, ROIC 24%&gt;&gt;WACC 6.5%, Insider Buy +€7.67M (AMF). Kein FLAG. Sparplan voll aktiv. Nächster Check: H1 2026 Report.  |  [LV 17.04.] v3.7 Live-Verify: Score 68 ±2 bestätigt (OpM 41,05% / Fwd P/E 34,91 + P/FCF 38x → beide Fix-1-Zweige hart 0). D4 durch Screener-Exception (ROIC 24% &gt;&gt; WACC +17,5pp) geschützt. Nach −8,4% Kursdrop Fwd P/E von 39→34,9.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>[V] Re-Analyse 07.04.: Score 65→67 (+2). Net Debt/EBITDA 3.6x→2.57x ✅. Fwd P/E 27x→19.9x ✅. ROIC 2.6% &lt; WACC bleibt Schwäche. FCF −13.4% YoY. Trigger 23.04.: FCF &gt;.3B nötig.</t>
+          <t>[V] Re-Analyse 07.04.: Score 65→67 (+2). Net Debt/EBITDA 3.6x→2.57x ✅. Fwd P/E 27x→19.9x ✅. ROIC 2.6% &lt; WACC bleibt Schwäche. FCF −13.4% YoY. Trigger 23.04.: FCF &gt;.3B nötig.  |  [LV 17.04.] v3.7 Live-Verify: Score 63 ±1 bestätigt (OpM 18,17% / Fwd P/E FY26 20,80 unter Schwelle → nur P/FCF 29,3x triggert Fix-1). Sell-Ratio 0% Warning. Q1 Earnings 23.04. kritisch.</t>
         </is>
       </c>
     </row>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4867771D-F266-4F4B-969D-734BD69A2AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC048F-1DB8-4ACC-B6A7-E81746AD30E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="232">
   <si>
     <t>🦅  DYNASTIEDEPOT – QUICKSCREEN AMPEL  |  18.04.2026 (v3.7 + Schema-Alignment)</t>
   </si>
@@ -349,19 +349,19 @@
     <t>Halbleiter-Equip</t>
   </si>
   <si>
-    <t>~42–50x [~]</t>
-  </si>
-  <si>
-    <t>~35% [~]</t>
-  </si>
-  <si>
-    <t>~51% [~]</t>
+    <t>48x [V 17.04.]</t>
+  </si>
+  <si>
+    <t>26.48% TTM [V 17.04.]</t>
+  </si>
+  <si>
+    <t>52.8% [V 17.04.]</t>
   </si>
   <si>
     <t>~16% [~]</t>
   </si>
   <si>
-    <t>9 / Wide ✅</t>
+    <t>9 / Wide</t>
   </si>
   <si>
     <t>n.a.</t>
@@ -373,7 +373,7 @@
     <t>68 / DEFCON 3</t>
   </si>
   <si>
-    <t>+2</t>
+    <t>+2 v3.5-&gt;v3.7</t>
   </si>
   <si>
     <t>🟡 DEFCON 3 / ✅ Volle Rate 33,53€ (D3=1.0 seit v3.4)</t>
@@ -385,7 +385,7 @@
     <t>17.04.2026</t>
   </si>
   <si>
-    <t>[V] DEFCON 3 (68/100). Moat 19/20 Wide Monopol, Fwd P/E 38x + P/FCF ~41x = Bewertungsprämie ohne Sicherheitsmarge. China-Revenue 14.7% → Kein Tariff-FLAG.  |  [LV 17.04.] v3.7 Live-Verify: Score 68 ±2 bestätigt (OpM 36,1% / Fwd P/E 39,52 + P/FCF 48x → beide Fix-1-Zweige hart 0). WATCH: Fwd P/E FY27 30,30 Grenzfall — bei &lt;30 nach Guidance Score +1-2 (D4-Upside).</t>
+    <t>[V 17.04.] Score 68. OpM 36,1%, Fwd P/E 39,52 + P/FCF 48x -&gt; QT-Fix-1 beide hart 0. ROIC 26,48% TTM. WATCH: Fwd P/E FY27 30,30 Grenzfall — bei &lt;30 Score +1-2 (D4-Upside).</t>
   </si>
   <si>
     <t>Broadcom Inc.</t>
@@ -397,12 +397,12 @@
     <t>~22x [KB]</t>
   </si>
   <si>
+    <t>&gt;20% [KB]</t>
+  </si>
+  <si>
     <t>~65% [KB]</t>
   </si>
   <si>
-    <t>~68% [KB]</t>
-  </si>
-  <si>
     <t>~21% [KB]</t>
   </si>
   <si>
@@ -412,7 +412,7 @@
     <t>84 / DEFCON 4</t>
   </si>
   <si>
-    <t>-2</t>
+    <t>-2 v3.5-&gt;v3.7</t>
   </si>
   <si>
     <t>⚠️ Insider-Check ausstehend (verm. Post-Vesting) | Sparplan läuft</t>
@@ -421,7 +421,7 @@
     <t>Q3 FY26 Earnings Jun 2026</t>
   </si>
   <si>
-    <t>[KB] Kalibrierungsanker 86/100. Fabless CapEx/OCF &lt;15%. AI-Backlog 3B. Insider-FLAG: 23M vermutl. Post-Vesting — OpenInsider-Check vor FLAG-Aktivierung Pflicht.</t>
+    <t>[KB] Kalibrierungsanker 86-&gt;84 (v3.7 Algebra). Fabless CapEx/OCF &lt;15%. AI-Backlog. Insider $123M unter Review — OpenInsider-Check vor FLAG-Aktivierung.</t>
   </si>
   <si>
     <t>Microsoft Corp.</t>
@@ -433,10 +433,10 @@
     <t>~38x [~]</t>
   </si>
   <si>
-    <t>~7.5% [V]</t>
-  </si>
-  <si>
-    <t>~70% [KB]</t>
+    <t>7.5% [V]</t>
+  </si>
+  <si>
+    <t>~69% [~]</t>
   </si>
   <si>
     <t>~13% [~]</t>
@@ -445,7 +445,7 @@
     <t>59 / DEFCON 2</t>
   </si>
   <si>
-    <t>-1</t>
+    <t>-1 v3.5-&gt;v3.7</t>
   </si>
   <si>
     <t>🔴 FLAG: CapEx/OCF &gt;60% | DEFCON 2 (59) | ⏸ Einfrieren</t>
@@ -454,7 +454,7 @@
     <t>29.04.2026 Q3 FY26 Earnings</t>
   </si>
   <si>
-    <t>[V] Re-Analyse 08.04.: Score 77→60 (−17). CapEx/OCF Q2 FY26 83.6% (bereinigt ~63%). ROIC 7.5% &lt; WACC 13.35%. FLAG aktiv. Re-Check 29.04.: bereinigtes CapEx/OCF &lt;60% = FLAG-Auflösung möglich.</t>
+    <t>[V] Re-Analyse 08.04.: 77-&gt;60 (-17). CapEx/OCF Q2 FY26 83,6% (bereinigt ~63%). ROIC 7,5% &lt; WACC 13,35%. FLAG aktiv. Re-Check 29.04. Q3 FY26 — bereinigtes CapEx/OCF &lt;60% = FLAG-Auflösung möglich.</t>
   </si>
   <si>
     <t>Costco Wholesale</t>
@@ -463,19 +463,19 @@
     <t>Einzelhandel</t>
   </si>
   <si>
-    <t>~50–55x [~]</t>
-  </si>
-  <si>
-    <t>~30% [~]</t>
-  </si>
-  <si>
-    <t>~13% ✅</t>
+    <t>~53x [~]</t>
+  </si>
+  <si>
+    <t>5.6% GAAP (MY 15.2%)</t>
+  </si>
+  <si>
+    <t>12.7%</t>
   </si>
   <si>
     <t>~10% [~]</t>
   </si>
   <si>
-    <t>8 / Wide ✅</t>
+    <t>8 / Wide</t>
   </si>
   <si>
     <t>Exception (GM)</t>
@@ -487,7 +487,7 @@
     <t>69 / DEFCON 3</t>
   </si>
   <si>
-    <t>0</t>
+    <t>0 v3.5-&gt;v3.7</t>
   </si>
   <si>
     <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | Screener-Exception Membership Yield 15.2% &gt; WACC</t>
@@ -496,7 +496,7 @@
     <t>28.05.2026</t>
   </si>
   <si>
-    <t>[~] Exception: GM ~13% strukturell (Membership-Fee). P/FCF &gt; 45x Exception aktiv. !Analysiere ausstehend.</t>
+    <t>[~] Exception: GM 12,7% strukturell (Membership-Fee). Membership-Yield 15,2% &gt; WACC 12,3% als ökonomischer Return. D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
     <t>Hermès Intl. (EUR)</t>
@@ -505,16 +505,16 @@
     <t>Luxus</t>
   </si>
   <si>
-    <t>~38x [V]</t>
-  </si>
-  <si>
-    <t>~22% [V]</t>
-  </si>
-  <si>
-    <t>~70% [V]</t>
-  </si>
-  <si>
-    <t>Wide [~]</t>
+    <t>38x [V]</t>
+  </si>
+  <si>
+    <t>24.2% TTM [V]</t>
+  </si>
+  <si>
+    <t>71% [V]</t>
+  </si>
+  <si>
+    <t>Wide [V]</t>
   </si>
   <si>
     <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | Screener-Exception ROIC 24% &gt;&gt; WACC</t>
@@ -523,7 +523,7 @@
     <t>H1 2026 Report Juli/Aug 2026</t>
   </si>
   <si>
-    <t>[V] Re-Analyse 15.04.2026: Score 71→69 (−2). Q1 2026: €4.07B (+6% CER, −1% reported). Miss vs. +7–8% Konsens. Kursreaktion −8.4% (€1.783→€1.632,50). 52W-Tief €1.529 intraday. Treiber: Mittlerer Osten −6% (Iran-Krieg, UAE Malls −40%), FX-Headwind €290M, China +2%. Positiv: Leder +9%, ROIC 24%&gt;&gt;WACC 6.5%, Insider Buy +€7.67M (AMF). Kein FLAG. Sparplan voll aktiv. Nächster Check: H1 2026 Report.  |  [LV 17.04.] v3.7 Live-Verify: Score 68 ±2 bestätigt (OpM 41,05% / Fwd P/E 34,91 + P/FCF 38x → beide Fix-1-Zweige hart 0). D4 durch Screener-Exception (ROIC 24% &gt;&gt; WACC +17,5pp) geschützt. Nach −8,4% Kursdrop Fwd P/E von 39→34,9.</t>
+    <t>[V] Re-Analyse 15.04.: 71-&gt;68 (Q1 Miss -8,4% Mittlerer Osten). ROIC 24% &gt;&gt; WACC 6,5% = Screener-Exception #3. Netto-Cash +9,89B EUR. D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
     <t>Healthcare-SW</t>
@@ -550,7 +550,7 @@
     <t>21.05.2026 Q1 FY27</t>
   </si>
   <si>
-    <t>[V] DEFCON 4 (74/100). Asset-light SaaS. Moat Wide (Switching Costs Life-Science). CapEx/OCF &lt;10%. Sparplan voll aktiv.</t>
+    <t>[V] Score 74 stabil. Asset-light SaaS. Moat Wide (Switching Costs Life-Science). CapEx/OCF &lt;10%. D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
     <t>Schneider Electric (EUR)</t>
@@ -559,72 +559,84 @@
     <t>Industrials</t>
   </si>
   <si>
-    <t>~20–25x [~]</t>
+    <t>10.48% TTM</t>
+  </si>
+  <si>
+    <t>~42% [~]</t>
+  </si>
+  <si>
+    <t>~11% [~]</t>
+  </si>
+  <si>
+    <t>Narrow/Wide</t>
+  </si>
+  <si>
+    <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | v3.7 Fix-3 Sell-Ratio</t>
+  </si>
+  <si>
+    <t>07.05.2026</t>
+  </si>
+  <si>
+    <t>[~] EUR-denominiert. ROIC 10,48% &gt; WACC 8,96%. Non-US IFRS. FCF-Wachstum +41% 3J. Schwächen: P/FCF 37,7x, Goodwill 40,2% (AVEVA). D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>Berkshire Hathaway B</t>
+  </si>
+  <si>
+    <t>Holding/Vers.</t>
+  </si>
+  <si>
+    <t>Exception (P/B 1.44x)</t>
+  </si>
+  <si>
+    <t>5.6-7.8% GAAP [Float]</t>
+  </si>
+  <si>
+    <t>n.a. (Holding)</t>
+  </si>
+  <si>
+    <t>~8% [~]</t>
+  </si>
+  <si>
+    <t>~1,5-1,6x P/B</t>
+  </si>
+  <si>
+    <t>75 / DEFCON 3</t>
+  </si>
+  <si>
+    <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | Insurance Exception (P/B 1.44x)</t>
+  </si>
+  <si>
+    <t>30.06.2026</t>
+  </si>
+  <si>
+    <t>[~] Insurance Exception: P/B 1,44x. Float $686B, BNSF, 60J Track-Record. Insider: Abel $15,3M Open-Market. CapEx/OCF 45,6% (BNSF+BHE, kein FLAG). D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>Visa Inc.</t>
+  </si>
+  <si>
+    <t>Payments</t>
+  </si>
+  <si>
+    <t>28.32x [V 18.04.]</t>
+  </si>
+  <si>
+    <t>9.89% GAAP &lt; WACC 10.48%</t>
+  </si>
+  <si>
+    <t>80.4% [V 18.04.]</t>
   </si>
   <si>
     <t>~12% [~]</t>
   </si>
   <si>
-    <t>~40% [~]</t>
-  </si>
-  <si>
-    <t>~11% [~]</t>
-  </si>
-  <si>
-    <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | v3.7 Fix-3 Sell-Ratio</t>
-  </si>
-  <si>
-    <t>07.05.2026</t>
-  </si>
-  <si>
-    <t>[~] EUR-denominiert. ROIC ~12% Grenzfall. Non-US IFRS. !Analysiere ausstehend. ADR: SBGSY.</t>
-  </si>
-  <si>
-    <t>Berkshire Hathaway B</t>
-  </si>
-  <si>
-    <t>Holding/Vers.</t>
-  </si>
-  <si>
-    <t>n.a.*</t>
-  </si>
-  <si>
-    <t>~8% [~]</t>
-  </si>
-  <si>
-    <t>~1,5–1,6x P/B</t>
-  </si>
-  <si>
-    <t>75 / DEFCON 3</t>
-  </si>
-  <si>
-    <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | Insurance Exception (P/B 1.44x)</t>
-  </si>
-  <si>
-    <t>30.06.2026</t>
-  </si>
-  <si>
-    <t>[~] Exception: P/B ~1.5–1.6x ✅ (&lt;1.5x = Kaufsignal Buffett). Float &gt;70B. Holding-Float-Logik aktiv.</t>
-  </si>
-  <si>
-    <t>Visa Inc.</t>
-  </si>
-  <si>
-    <t>Payments</t>
-  </si>
-  <si>
-    <t>~28–32x [~]</t>
-  </si>
-  <si>
-    <t>~45% [~]</t>
-  </si>
-  <si>
-    <t>~80% [KB]</t>
-  </si>
-  <si>
     <t>63 / DEFCON 2</t>
   </si>
   <si>
+    <t>-23 Backfill-&gt;Forward</t>
+  </si>
+  <si>
     <t>🟠 DEFCON 2 / ⏸ Sockelbetrag 17,81€ | Forward 18.04. nach Advisor-Review (86→72→63)</t>
   </si>
   <si>
@@ -634,7 +646,7 @@
     <t>18.04.2026</t>
   </si>
   <si>
-    <t>[V 18.04.] Forward-Vollanalyse + Rescoring nach Advisor-Review: 86→72→63 (-23). Drei Sub-Score-Korrekturen: (1) Moat Pricing-Power-Bonus entfernt (Transcript nicht verifiziert), (2) Insider Ownership 2→1 (V &lt;1% Threshold strikt), (3) ROIC 8→1 (Regel-4-Gating greift nicht: GW/Assets 19,95% &lt;30%, GAAP 9,89% &lt; WACC 10,48%). Technicals-Kollaps (RelStärke -13,97pp vs SPY, Kurs -4,97% unter fallendem 200MA). Q2 FY26 28.04. entscheidet D2-Pfad.</t>
+    <t>[V 18.04.] Forward-Vollanalyse + Rescoring nach Advisor: 86-&gt;72-&gt;63. DREI Sub-Score-Korrekturen: (1) Moat Pricing-Power-Bonus entfernt (Transcript-Regel); (2) Insider Ownership 2-&gt;1 (V &lt;1% strikt); (3) ROIC 8-&gt;1 (Regel-4-Gating GW/Assets 19,95% &lt;30% greift NICHT, GAAP 9,89% &lt; WACC 10,48%). Technicals-Kollaps (RelStärke -13,97pp vs SPY, Kurs -4,97% unter fallendem 200MA). Q2 FY26 28.04. D2-Entscheidung.</t>
   </si>
   <si>
     <t>Thermo Fisher Sci.</t>
@@ -643,10 +655,13 @@
     <t>Life Sciences</t>
   </si>
   <si>
-    <t>~29x [V]</t>
-  </si>
-  <si>
-    <t>~9% [V]</t>
+    <t>31.10x [V 18.04.]</t>
+  </si>
+  <si>
+    <t>17.18% bereinigt (Regel-4)</t>
+  </si>
+  <si>
+    <t>40.9% [V 18.04.]</t>
   </si>
   <si>
     <t>~4% [~]</t>
@@ -655,13 +670,16 @@
     <t>64 / DEFCON 2</t>
   </si>
   <si>
+    <t>+1 Backfill-&gt;Forward</t>
+  </si>
+  <si>
     <t>🟠 DEFCON 2 / ⏸ Sockelbetrag 17,81€ | fcf_trend_neg Disclosure (Option B)</t>
   </si>
   <si>
     <t>23.04.2026 Q1 Earnings</t>
   </si>
   <si>
-    <t>[V 18.04.] Forward-Vollanalyse: Score 64 (Algebra 63 ±1 empirisch bestätigt). ROIC bereinigt 17,18% vs WACC 10,44% = +6,74pp (Regel-4-Gating greift: GW/Assets 44,74% ≥30%, IC bereinigt 43,430M). fcf_trend_neg schema-getriggert (FY25 FCF -13,4% YoY, CapEx +8,9%) aber NICHT aktiviert (Option B Advisor): WC-Delta -1,766M &gt; FCF-Delta -974M = WC-Noise; 4J-Plateau $6,9→6,9→7,3→6,3B; OpInc +5,1%. Q1 23.04. = Resolve-Gate.</t>
+    <t>[V 18.04.] Forward-Vollanalyse: Score 64 (Algebra 63 empirisch +/-1). ROIC bereinigt 17,18% vs WACC 10,44% = +6,74pp (Regel-4-Gating greift: GW/Assets 44,74% &gt;=30%, IC bereinigt 43,430M). fcf_trend_neg schema-getriggert (FY25 FCF -13,4% YoY, CapEx +8,9%) aber NICHT aktiviert per Advisor (Option B): WC-Delta -1,766M &gt; FCF-Delta -974M = WC-Noise; 4J-Plateau 6,9-&gt;6,9-&gt;7,3-&gt;6,3B; OpInc +5,1%. Q1 23.04. = Resolve-Gate.</t>
   </si>
   <si>
     <t>Amphenol Corp.</t>
@@ -670,13 +688,13 @@
     <t>Steckverbinder</t>
   </si>
   <si>
-    <t>~25–30x [~]</t>
+    <t>~28x [~]</t>
   </si>
   <si>
     <t>~22% [~]</t>
   </si>
   <si>
-    <t>~34% [~]</t>
+    <t>~32% [V]</t>
   </si>
   <si>
     <t>~18% [~]</t>
@@ -688,7 +706,7 @@
     <t>Q2 2025 Earnings 23.07.2025</t>
   </si>
   <si>
-    <t>[V+TC] DEFCON 3 (63/100). FLAG aktiv (Score-basiert). Tariff-Check 15.04.: China Revenue 14.7% &lt; 15%-Schwelle → kein Revenue-FLAG. Supply-Chain CN/MY bestätigt (CEO Q1 2025 Call). Risk-Map-Notiz aktiv.</t>
+    <t>[V+TC] DEFCON 2 seit 18.04. Schema-Alignment. FLAG aktiv (Score-basiert 63 + D2). Tariff-Check 15.04.: China Rev 14,7% &lt; 15%-Schwelle -&gt; kein Revenue-FLAG. Supply-Chain CN/MY Risk-Map aktiv. Sparrate 0€.</t>
   </si>
   <si>
     <t>Sparrate-Check</t>
@@ -1023,7 +1041,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="19">
     <dxf>
       <font>
         <b/>
@@ -1066,35 +1084,78 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <sz val="9"/>
+        <color rgb="FF276221"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <sz val="9"/>
+        <color rgb="FF276221"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFCC0000"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE0E0"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF843C0C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1130,30 +1191,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFEBF3FF"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF843C0C"/>
+      </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF276221"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFD6F0DA"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1923,19 +2000,19 @@
         <v>172</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>108</v>
@@ -1979,40 +2056,40 @@
         <v>181</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>92</v>
+        <v>183</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>158</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>147</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>149</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O14" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q14" s="25" t="s">
         <v>114</v>
@@ -2021,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2029,22 +2106,22 @@
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>107</v>
@@ -2056,28 +2133,28 @@
         <v>109</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="M15" s="5">
-        <v>-23</v>
+        <v>197</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O15" s="8">
         <v>17.809999999999999</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R15" s="5">
         <v>0</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2085,22 +2162,22 @@
         <v>67</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>158</v>
@@ -2112,28 +2189,28 @@
         <v>109</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="M16" s="11">
-        <v>-3</v>
+        <v>209</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>210</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="O16" s="15">
         <v>17.809999999999999</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q16" s="25" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R16" s="11">
         <v>0</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2141,25 +2218,25 @@
         <v>37</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>108</v>
@@ -2168,19 +2245,19 @@
         <v>109</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>111</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q17" s="24" t="s">
         <v>114</v>
@@ -2189,12 +2266,12 @@
         <v>0</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="38" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
@@ -2207,10 +2284,10 @@
       <c r="K18" s="27"/>
       <c r="L18" s="28"/>
       <c r="M18" s="16" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O18" s="18">
         <f>SUM(O7:O17)</f>
@@ -2219,7 +2296,7 @@
     </row>
     <row r="20" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
@@ -2241,7 +2318,7 @@
     </row>
     <row r="21" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -2263,7 +2340,7 @@
     </row>
     <row r="22" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
@@ -2285,7 +2362,7 @@
     </row>
     <row r="23" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="26" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
@@ -2307,7 +2384,7 @@
     </row>
     <row r="24" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="26" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
@@ -2329,7 +2406,7 @@
     </row>
     <row r="25" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="26" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
@@ -2367,39 +2444,51 @@
     <mergeCell ref="B18:L18"/>
   </mergeCells>
   <conditionalFormatting sqref="L7:L17">
-    <cfRule type="expression" dxfId="14" priority="13">
+    <cfRule type="expression" dxfId="18" priority="16" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("DEFCON 4",L7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="17" priority="17" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("DEFCON 3",L7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="16" priority="18" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("DEFCON 2",L7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="16">
-      <formula>ISNUMBER(SEARCH("QS-OK",L7))</formula>
+    <cfRule type="expression" dxfId="15" priority="19" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("DEFCON 1",L7))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M17">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N17">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="11" priority="20" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("FLAG",N7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="10" priority="21" stopIfTrue="1">
+      <formula>LEFT(N7,1)="🔴"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="22" stopIfTrue="1">
+      <formula>LEFT(N7,1)="🟠"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="23" stopIfTrue="1">
+      <formula>LEFT(N7,1)="🟡"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="24" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("DEFCON 3",N7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="6" priority="25" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("Halten",N7))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="26" stopIfTrue="1">
+      <formula>LEFT(N7,1)="🟢"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O17">

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobia\OneDrive\Desktop\Claude Stuff\03_Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFC048F-1DB8-4ACC-B6A7-E81746AD30E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F061BB4B-B805-48C6-A0EF-4FF31F79E233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Satelliten Monitor" sheetId="1" r:id="rId1"/>
@@ -36,259 +36,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="232">
   <si>
-    <t>🦅  DYNASTIEDEPOT – QUICKSCREEN AMPEL  |  18.04.2026 (v3.7 + Schema-Alignment)</t>
-  </si>
-  <si>
-    <t>Filter: P/FCF ≤35x 🟢 / ≤45x 🟡 / &gt;45x 🔴  |  ROIC ≥15% 🟢 / ≥12% 🟡 / &lt;12% 🔴  |  Moat Wide 🟢 / Narrow 🟡 / None 🔴  |  FLAG überschreibt immer → 🔴</t>
+    <t>🦅  DYNASTIEDEPOT – SATELLITEN MONITOR v2.0</t>
+  </si>
+  <si>
+    <t>Stand: 18.04.2026  |  Broker: Scalable Capital  |  Slots: 11/11</t>
+  </si>
+  <si>
+    <t>Sparrate Satelliten: 285 €/Monat  |  D4/D3-Rate: 35,63€  |  D2-Sockelbetrag: 17,81€ (50%)  |  Nenner 8.0 (v3.7 + Schema-SKILL-Threshold-Alignment 18.04.)</t>
+  </si>
+  <si>
+    <t>Vollanalysiert: 11 / 11 ✅  |  Geschätzt: 0 / 11</t>
+  </si>
+  <si>
+    <t>Eingefroren: MSFT (🔴 FLAG CapEx/OCF, D2) | APH (🔴 FLAG Score-basiert, D2 seit 18.04.) — Sparrate 0€</t>
+  </si>
+  <si>
+    <t>Ergebnis: 🟢 7 Voll  🟠 2 D2-Sockelbetrag (V, TMO)  🔴 2 Eingefroren (MSFT, APH)</t>
+  </si>
+  <si>
+    <t>Quellen: Vollanalyse [V] | Kalibrierungsanalyse [KB] | Schätzung [~] | Tariff-Check [TC]</t>
   </si>
   <si>
     <t>Ticker</t>
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>P/FCF Filter</t>
-  </si>
-  <si>
-    <t>ROIC Filter</t>
-  </si>
-  <si>
-    <t>Moat Filter</t>
-  </si>
-  <si>
-    <t>FLAG</t>
-  </si>
-  <si>
-    <t>Gesamt-Ampel</t>
-  </si>
-  <si>
-    <t>Nächster Schritt</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>Broadcom</t>
-  </si>
-  <si>
-    <t>🟢 ~22x</t>
-  </si>
-  <si>
-    <t>🟢 ~65%</t>
-  </si>
-  <si>
-    <t>🟢 Wide</t>
-  </si>
-  <si>
-    <t>✅</t>
-  </si>
-  <si>
-    <t>🟢 HALTEN</t>
-  </si>
-  <si>
-    <t>Sparplan aktiv. Kalibrierungsanker.</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>Costco</t>
-  </si>
-  <si>
-    <t>🟢 Exception</t>
-  </si>
-  <si>
-    <t>🟢 ~30%</t>
-  </si>
-  <si>
-    <t>Exception. Membership-Moat ✅. D4→D3 Schema-Alignment 18.04. Volle Rate 35,63€.</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>🟢 ~28–32x</t>
-  </si>
-  <si>
-    <t>🟢 ~45%</t>
-  </si>
-  <si>
-    <t>🟠 DEFCON 2 / ⏸ Sockelbetrag</t>
-  </si>
-  <si>
-    <t>Score 63 (Forward 18.04., -23 vs Backfill). Technicals-Kollaps + ROIC GAAP &lt; WACC. Sockelbetrag 17,81€. Q2 28.04.</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>Schneider Elec.</t>
-  </si>
-  <si>
-    <t>🟢 ~20–25x</t>
-  </si>
-  <si>
-    <t>🟡 ~12%</t>
-  </si>
-  <si>
-    <t>ROIC Grenzfall. D4→D3 Schema-Alignment 18.04. Volle Rate 35,63€.</t>
-  </si>
-  <si>
-    <t>BRK.B</t>
-  </si>
-  <si>
-    <t>Berkshire B</t>
-  </si>
-  <si>
-    <t>Exception. P/B ~1,5–1,6x ✅. D4→D3 Schema-Alignment 18.04. Volle Rate 35,63€.</t>
-  </si>
-  <si>
-    <t>APH</t>
-  </si>
-  <si>
-    <t>Amphenol</t>
-  </si>
-  <si>
-    <t>🟢 ~25–30x</t>
-  </si>
-  <si>
-    <t>🟢 ~22%</t>
-  </si>
-  <si>
-    <t>🔴 FLAG (Score)</t>
-  </si>
-  <si>
-    <t>🔴 FLAG / ⏸ EINGEFROREN</t>
-  </si>
-  <si>
-    <t>Score 63 (DEFCON 2 seit 18.04. Schema-Alignment). FLAG aktiv (Score-basiert). Tariff-Check CN 14.7% Risk-Map. Sparrate 0€.</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>ASML Holding</t>
-  </si>
-  <si>
-    <t>🟡 ~42–50x</t>
-  </si>
-  <si>
-    <t>🟢 ~35%</t>
-  </si>
-  <si>
-    <t>🟡 PRÜFEN</t>
-  </si>
-  <si>
-    <t>DEFCON 3 (68, v3.7 +2). Moat 19/20 Wide. v3.7 Fix-1: Fwd P/E + P/FCF Subscore-Deckel. Volle Rate 33,53€.</t>
-  </si>
-  <si>
-    <t>RMS</t>
-  </si>
-  <si>
-    <t>Hermès</t>
-  </si>
-  <si>
-    <t>🟡 ~38x</t>
-  </si>
-  <si>
-    <t>🟢 ~40%</t>
-  </si>
-  <si>
-    <t>v3.7: Score 68 (D4→D3 Schema-Alignment 18.04.). Screener-Exception ROIC 24% &gt;&gt; WACC. Volle Rate 35,63€.</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>Veeva Systems</t>
-  </si>
-  <si>
-    <t>🟡 ~45x</t>
-  </si>
-  <si>
-    <t>🟡 ~18%</t>
-  </si>
-  <si>
-    <t>v3.7: Score 74 (D4→D3 Schema-Alignment 18.04.). SaaS Wide Moat. Volle Rate 35,63€.</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>🟡 ~35–38x</t>
-  </si>
-  <si>
-    <t>🔴 ~7.5%</t>
-  </si>
-  <si>
-    <t>🔴 FLAG</t>
-  </si>
-  <si>
-    <t>🔴 FLAG / DEFCON 2 / ⏸ EINFRIEREN</t>
-  </si>
-  <si>
-    <t>Score 59 (↓1 v3.7). DEFCON 2. FLAG CapEx/OCF &gt;60% (bereinigt ~63%). ROIC 7.5% &lt; WACC. Re-Check 29.04.</t>
-  </si>
-  <si>
-    <t>TMO</t>
-  </si>
-  <si>
-    <t>Thermo Fisher</t>
-  </si>
-  <si>
-    <t>🟢 ~28x</t>
-  </si>
-  <si>
-    <t>🔴 ~9%</t>
-  </si>
-  <si>
-    <t>🟠 DEFCON 2 / ⏸ D2-SOCKELBETRAG</t>
-  </si>
-  <si>
-    <t>Score 64 (Forward 18.04., Algebra +1). ROIC bereinigt 17,2% (Regel-4). fcf_trend_neg struktureller Disclosure (Option B, WC-Noise). Sockelbetrag 17,81€. Q1 23.04.</t>
-  </si>
-  <si>
-    <t>LEGENDE</t>
-  </si>
-  <si>
-    <t>🟢 HALTEN: Alle 3 Filter grün + kein FLAG → Sparplan aktiv</t>
-  </si>
-  <si>
-    <t>🟡 PRÜFEN: Mind. 1 Filter gelb + kein FLAG → Halten, erhöhtes Monitoring</t>
-  </si>
-  <si>
-    <t>🔴 EINGEFROREN: FLAG aktiv (MSFT, APH) → Sparrate = 0€, Re-Analyse Pflicht</t>
-  </si>
-  <si>
-    <t>Exception-Logik: COST (GM strukturell ~13%), BRK.B (P/B statt P/FCF) → zählen als grün | Stand: 17.04.2026</t>
-  </si>
-  <si>
-    <t>🦅  DYNASTIEDEPOT – SATELLITEN MONITOR v2.0</t>
-  </si>
-  <si>
-    <t>Stand: 18.04.2026  |  Broker: Scalable Capital  |  Slots: 11/11</t>
-  </si>
-  <si>
-    <t>Sparrate Satelliten: 285 €/Monat  |  D4/D3-Rate: 35,63€  |  D2-Sockelbetrag: 17,81€ (50%)  |  Nenner 8.0 (v3.7 + Schema-SKILL-Threshold-Alignment 18.04.)</t>
-  </si>
-  <si>
-    <t>Vollanalysiert: 11 / 11 ✅  |  Geschätzt: 0 / 11</t>
-  </si>
-  <si>
-    <t>Eingefroren: MSFT (🔴 FLAG CapEx/OCF, D2) | APH (🔴 FLAG Score-basiert, D2 seit 18.04.) — Sparrate 0€</t>
-  </si>
-  <si>
-    <t>Ergebnis: 🟢 7 Voll  🟠 2 D2-Sockelbetrag (V, TMO)  🔴 2 Eingefroren (MSFT, APH)</t>
-  </si>
-  <si>
-    <t>Quellen: Vollanalyse [V] | Kalibrierungsanalyse [KB] | Schätzung [~] | Tariff-Check [TC]</t>
   </si>
   <si>
     <t>Sektor</t>
@@ -343,6 +115,9 @@
     <t>Hinweis</t>
   </si>
   <si>
+    <t>ASML</t>
+  </si>
+  <si>
     <t>ASML Holding NV</t>
   </si>
   <si>
@@ -388,6 +163,9 @@
     <t>[V 17.04.] Score 68. OpM 36,1%, Fwd P/E 39,52 + P/FCF 48x -&gt; QT-Fix-1 beide hart 0. ROIC 26,48% TTM. WATCH: Fwd P/E FY27 30,30 Grenzfall — bei &lt;30 Score +1-2 (D4-Upside).</t>
   </si>
   <si>
+    <t>AVGO</t>
+  </si>
+  <si>
     <t>Broadcom Inc.</t>
   </si>
   <si>
@@ -424,6 +202,9 @@
     <t>[KB] Kalibrierungsanker 86-&gt;84 (v3.7 Algebra). Fabless CapEx/OCF &lt;15%. AI-Backlog. Insider $123M unter Review — OpenInsider-Check vor FLAG-Aktivierung.</t>
   </si>
   <si>
+    <t>MSFT</t>
+  </si>
+  <si>
     <t>Microsoft Corp.</t>
   </si>
   <si>
@@ -457,6 +238,9 @@
     <t>[V] Re-Analyse 08.04.: 77-&gt;60 (-17). CapEx/OCF Q2 FY26 83,6% (bereinigt ~63%). ROIC 7,5% &lt; WACC 13,35%. FLAG aktiv. Re-Check 29.04. Q3 FY26 — bereinigtes CapEx/OCF &lt;60% = FLAG-Auflösung möglich.</t>
   </si>
   <si>
+    <t>COST</t>
+  </si>
+  <si>
     <t>Costco Wholesale</t>
   </si>
   <si>
@@ -499,6 +283,9 @@
     <t>[~] Exception: GM 12,7% strukturell (Membership-Fee). Membership-Yield 15,2% &gt; WACC 12,3% als ökonomischer Return. D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
+    <t>RMS</t>
+  </si>
+  <si>
     <t>Hermès Intl. (EUR)</t>
   </si>
   <si>
@@ -526,6 +313,12 @@
     <t>[V] Re-Analyse 15.04.: 71-&gt;68 (Q1 Miss -8,4% Mittlerer Osten). ROIC 24% &gt;&gt; WACC 6,5% = Screener-Exception #3. Netto-Cash +9,89B EUR. D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>Veeva Systems</t>
+  </si>
+  <si>
     <t>Healthcare-SW</t>
   </si>
   <si>
@@ -553,6 +346,9 @@
     <t>[V] Score 74 stabil. Asset-light SaaS. Moat Wide (Switching Costs Life-Science). CapEx/OCF &lt;10%. D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
+    <t>SU</t>
+  </si>
+  <si>
     <t>Schneider Electric (EUR)</t>
   </si>
   <si>
@@ -580,6 +376,9 @@
     <t>[~] EUR-denominiert. ROIC 10,48% &gt; WACC 8,96%. Non-US IFRS. FCF-Wachstum +41% 3J. Schwächen: P/FCF 37,7x, Goodwill 40,2% (AVEVA). D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
+    <t>BRK.B</t>
+  </si>
+  <si>
     <t>Berkshire Hathaway B</t>
   </si>
   <si>
@@ -613,6 +412,9 @@
     <t>[~] Insurance Exception: P/B 1,44x. Float $686B, BNSF, 60J Track-Record. Insider: Abel $15,3M Open-Market. CapEx/OCF 45,6% (BNSF+BHE, kein FLAG). D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
   </si>
   <si>
+    <t>V</t>
+  </si>
+  <si>
     <t>Visa Inc.</t>
   </si>
   <si>
@@ -649,6 +451,9 @@
     <t>[V 18.04.] Forward-Vollanalyse + Rescoring nach Advisor: 86-&gt;72-&gt;63. DREI Sub-Score-Korrekturen: (1) Moat Pricing-Power-Bonus entfernt (Transcript-Regel); (2) Insider Ownership 2-&gt;1 (V &lt;1% strikt); (3) ROIC 8-&gt;1 (Regel-4-Gating GW/Assets 19,95% &lt;30% greift NICHT, GAAP 9,89% &lt; WACC 10,48%). Technicals-Kollaps (RelStärke -13,97pp vs SPY, Kurs -4,97% unter fallendem 200MA). Q2 FY26 28.04. D2-Entscheidung.</t>
   </si>
   <si>
+    <t>TMO</t>
+  </si>
+  <si>
     <t>Thermo Fisher Sci.</t>
   </si>
   <si>
@@ -682,6 +487,9 @@
     <t>[V 18.04.] Forward-Vollanalyse: Score 64 (Algebra 63 empirisch +/-1). ROIC bereinigt 17,18% vs WACC 10,44% = +6,74pp (Regel-4-Gating greift: GW/Assets 44,74% &gt;=30%, IC bereinigt 43,430M). fcf_trend_neg schema-getriggert (FY25 FCF -13,4% YoY, CapEx +8,9%) aber NICHT aktiviert per Advisor (Option B): WC-Delta -1,766M &gt; FCF-Delta -974M = WC-Noise; 4J-Plateau 6,9-&gt;6,9-&gt;7,3-&gt;6,3B; OpInc +5,1%. Q1 23.04. = Resolve-Gate.</t>
   </si>
   <si>
+    <t>APH</t>
+  </si>
+  <si>
     <t>Amphenol Corp.</t>
   </si>
   <si>
@@ -734,6 +542,198 @@
   </si>
   <si>
     <t>🟢 Volle Rate 35,63€ (7 Positionen): ASML/COST/RMS/VEEV/SU/BRK.B D3, AVGO D4  |  🟠 D2-Sockelbetrag 17,81€ (2): V, TMO</t>
+  </si>
+  <si>
+    <t>🦅  DYNASTIEDEPOT – QUICKSCREEN AMPEL  |  18.04.2026 (v3.7 + Schema-Alignment)</t>
+  </si>
+  <si>
+    <t>Filter: P/FCF ≤35x 🟢 / ≤45x 🟡 / &gt;45x 🔴  |  ROIC ≥15% 🟢 / ≥12% 🟡 / &lt;12% 🔴  |  Moat Wide 🟢 / Narrow 🟡 / None 🔴  |  FLAG überschreibt immer → 🔴</t>
+  </si>
+  <si>
+    <t>P/FCF Filter</t>
+  </si>
+  <si>
+    <t>ROIC Filter</t>
+  </si>
+  <si>
+    <t>Moat Filter</t>
+  </si>
+  <si>
+    <t>FLAG</t>
+  </si>
+  <si>
+    <t>Gesamt-Ampel</t>
+  </si>
+  <si>
+    <t>Nächster Schritt</t>
+  </si>
+  <si>
+    <t>Broadcom</t>
+  </si>
+  <si>
+    <t>🟢 ~22x</t>
+  </si>
+  <si>
+    <t>🟢 ~65%</t>
+  </si>
+  <si>
+    <t>🟢 Wide</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>🟢 HALTEN</t>
+  </si>
+  <si>
+    <t>Sparplan aktiv. Kalibrierungsanker.</t>
+  </si>
+  <si>
+    <t>Costco</t>
+  </si>
+  <si>
+    <t>🟢 Exception</t>
+  </si>
+  <si>
+    <t>🟢 ~30%</t>
+  </si>
+  <si>
+    <t>Exception. Membership-Moat ✅. D4→D3 Schema-Alignment 18.04. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>🟢 ~28–32x</t>
+  </si>
+  <si>
+    <t>🟢 ~45%</t>
+  </si>
+  <si>
+    <t>🟠 DEFCON 2 / ⏸ Sockelbetrag</t>
+  </si>
+  <si>
+    <t>Score 63 (Forward 18.04., -23 vs Backfill). Technicals-Kollaps + ROIC GAAP &lt; WACC. Sockelbetrag 17,81€. Q2 28.04.</t>
+  </si>
+  <si>
+    <t>Schneider Elec.</t>
+  </si>
+  <si>
+    <t>🟢 ~20–25x</t>
+  </si>
+  <si>
+    <t>🟡 ~12%</t>
+  </si>
+  <si>
+    <t>ROIC Grenzfall. D4→D3 Schema-Alignment 18.04. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>Berkshire B</t>
+  </si>
+  <si>
+    <t>Exception. P/B ~1,5–1,6x ✅. D4→D3 Schema-Alignment 18.04. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>Amphenol</t>
+  </si>
+  <si>
+    <t>🟢 ~25–30x</t>
+  </si>
+  <si>
+    <t>🟢 ~22%</t>
+  </si>
+  <si>
+    <t>🔴 FLAG (Score)</t>
+  </si>
+  <si>
+    <t>🔴 FLAG / ⏸ EINGEFROREN</t>
+  </si>
+  <si>
+    <t>Score 63 (DEFCON 2 seit 18.04. Schema-Alignment). FLAG aktiv (Score-basiert). Tariff-Check CN 14.7% Risk-Map. Sparrate 0€.</t>
+  </si>
+  <si>
+    <t>ASML Holding</t>
+  </si>
+  <si>
+    <t>🟡 ~42–50x</t>
+  </si>
+  <si>
+    <t>🟢 ~35%</t>
+  </si>
+  <si>
+    <t>🟡 PRÜFEN</t>
+  </si>
+  <si>
+    <t>DEFCON 3 (68, v3.7 +2). Moat 19/20 Wide. v3.7 Fix-1: Fwd P/E + P/FCF Subscore-Deckel. Volle Rate 33,53€.</t>
+  </si>
+  <si>
+    <t>Hermès</t>
+  </si>
+  <si>
+    <t>🟡 ~38x</t>
+  </si>
+  <si>
+    <t>🟢 ~40%</t>
+  </si>
+  <si>
+    <t>v3.7: Score 68 (D4→D3 Schema-Alignment 18.04.). Screener-Exception ROIC 24% &gt;&gt; WACC. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>🟡 ~45x</t>
+  </si>
+  <si>
+    <t>🟡 ~18%</t>
+  </si>
+  <si>
+    <t>v3.7: Score 74 (D4→D3 Schema-Alignment 18.04.). SaaS Wide Moat. Volle Rate 35,63€.</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>🟡 ~35–38x</t>
+  </si>
+  <si>
+    <t>🔴 ~7.5%</t>
+  </si>
+  <si>
+    <t>🔴 FLAG</t>
+  </si>
+  <si>
+    <t>🔴 FLAG / DEFCON 2 / ⏸ EINFRIEREN</t>
+  </si>
+  <si>
+    <t>Score 59 (↓1 v3.7). DEFCON 2. FLAG CapEx/OCF &gt;60% (bereinigt ~63%). ROIC 7.5% &lt; WACC. Re-Check 29.04.</t>
+  </si>
+  <si>
+    <t>Thermo Fisher</t>
+  </si>
+  <si>
+    <t>🟢 ~28x</t>
+  </si>
+  <si>
+    <t>🔴 ~9%</t>
+  </si>
+  <si>
+    <t>🟠 DEFCON 2 / ⏸ D2-SOCKELBETRAG</t>
+  </si>
+  <si>
+    <t>Score 64 (Forward 18.04., Algebra +1). ROIC bereinigt 17,2% (Regel-4). fcf_trend_neg struktureller Disclosure (Option B, WC-Noise). Sockelbetrag 17,81€. Q1 23.04.</t>
+  </si>
+  <si>
+    <t>LEGENDE</t>
+  </si>
+  <si>
+    <t>🟢 HALTEN: Alle 3 Filter grün + kein FLAG → Sparplan aktiv</t>
+  </si>
+  <si>
+    <t>🟡 PRÜFEN: Mind. 1 Filter gelb + kein FLAG → Halten, erhöhtes Monitoring</t>
+  </si>
+  <si>
+    <t>🔴 EINGEFROREN: FLAG aktiv (MSFT, APH) → Sparrate = 0€, Re-Analyse Pflicht</t>
+  </si>
+  <si>
+    <t>Exception-Logik: COST (GM strukturell ~13%), BRK.B (P/B statt P/FCF) → zählen als grün | Stand: 17.04.2026</t>
   </si>
 </sst>
 </file>
@@ -1009,33 +1009,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1523,8 +1523,8 @@
   <sheetData>
     <row r="1" spans="2:19" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="37" t="s">
-        <v>78</v>
+      <c r="B2" s="35" t="s">
+        <v>0</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -1538,37 +1538,37 @@
       <c r="L2" s="30"/>
       <c r="M2" s="30"/>
       <c r="N2" s="30"/>
-      <c r="O2" s="33" t="s">
-        <v>79</v>
+      <c r="O2" s="31" t="s">
+        <v>1</v>
       </c>
       <c r="P2" s="30"/>
       <c r="Q2" s="30"/>
       <c r="R2" s="30"/>
       <c r="S2" s="30"/>
     </row>
-    <row r="3" spans="2:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
-        <v>80</v>
+    <row r="3" spans="2:19" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="29" t="s">
+        <v>2</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
-      <c r="E3" s="35" t="s">
-        <v>81</v>
+      <c r="E3" s="33" t="s">
+        <v>3</v>
       </c>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
-      <c r="H3" s="35" t="s">
-        <v>82</v>
+      <c r="H3" s="33" t="s">
+        <v>4</v>
       </c>
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
-      <c r="K3" s="35" t="s">
-        <v>83</v>
+      <c r="K3" s="33" t="s">
+        <v>5</v>
       </c>
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
-      <c r="N3" s="36" t="s">
-        <v>84</v>
+      <c r="N3" s="34" t="s">
+        <v>6</v>
       </c>
       <c r="O3" s="30"/>
       <c r="P3" s="30"/>
@@ -1598,680 +1598,680 @@
     </row>
     <row r="5" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="O7" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R7" s="5">
         <v>0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="O8" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R8" s="11">
         <v>0</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="I9" s="5" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="O9" s="15">
         <v>0</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R9" s="5">
         <v>0</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="O10" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="25" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R10" s="11">
         <v>0</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="O11" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R11" s="5">
         <v>0</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>161</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>162</v>
+        <v>93</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="O12" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="25" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R12" s="11">
         <v>0</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>170</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>177</v>
       </c>
       <c r="O13" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R13" s="5">
         <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>183</v>
+        <v>116</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>186</v>
+        <v>119</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="O14" s="8">
         <v>35.630000000000003</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="Q14" s="25" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R14" s="11">
         <v>0</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>190</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="O15" s="8">
         <v>17.809999999999999</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="R15" s="5">
         <v>0</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>207</v>
+        <v>142</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="O16" s="15">
         <v>17.809999999999999</v>
       </c>
       <c r="P16" s="11" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="Q16" s="25" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="R16" s="11">
         <v>0</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>213</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="141.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>214</v>
+        <v>150</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>215</v>
+        <v>151</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="O17" s="8">
         <v>0</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R17" s="5">
         <v>0</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>222</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="38" t="s">
-        <v>223</v>
+      <c r="B18" s="36" t="s">
+        <v>159</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
@@ -2284,10 +2284,10 @@
       <c r="K18" s="27"/>
       <c r="L18" s="28"/>
       <c r="M18" s="16" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="O18" s="18">
         <f>SUM(O7:O17)</f>
@@ -2295,8 +2295,8 @@
       </c>
     </row>
     <row r="20" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="34" t="s">
-        <v>226</v>
+      <c r="B20" s="32" t="s">
+        <v>162</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="21" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="22" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="23" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="26" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="24" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="26" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="25" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="26" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
@@ -2470,10 +2470,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N17">
     <cfRule type="expression" dxfId="11" priority="20" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("FLAG",N7))</formula>
+      <formula>LEFT(N7,1)="🔴"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="21" stopIfTrue="1">
-      <formula>LEFT(N7,1)="🔴"</formula>
+      <formula>ISNUMBER(SEARCH("FLAG",N7))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="22" stopIfTrue="1">
       <formula>LEFT(N7,1)="🟠"</formula>
@@ -2485,10 +2485,10 @@
       <formula>ISNUMBER(SEARCH("DEFCON 3",N7))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="25" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("Halten",N7))</formula>
+      <formula>LEFT(N7,1)="🟢"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="26" stopIfTrue="1">
-      <formula>LEFT(N7,1)="🟢"</formula>
+      <formula>ISNUMBER(SEARCH("Halten",N7))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O17">
@@ -2533,8 +2533,8 @@
   <sheetData>
     <row r="1" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
-        <v>0</v>
+      <c r="B2" s="37" t="s">
+        <v>168</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -2545,8 +2545,8 @@
       <c r="I2" s="30"/>
     </row>
     <row r="3" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
-        <v>1</v>
+      <c r="B3" s="29" t="s">
+        <v>169</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
@@ -2559,319 +2559,319 @@
     <row r="4" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
+        <v>171</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>17</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>22</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>33</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>36</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>41</v>
+        <v>201</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>43</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>48</v>
+        <v>207</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>49</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>51</v>
+        <v>209</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>57</v>
+        <v>213</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>62</v>
+        <v>217</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>64</v>
+        <v>219</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>69</v>
+        <v>223</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>71</v>
+        <v>225</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="32" t="s">
-        <v>73</v>
+      <c r="B19" s="38" t="s">
+        <v>227</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="20" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="26" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="26" t="s">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="26" t="s">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="\€#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -225,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -332,6 +333,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1042,13 +1055,12 @@
           <t>Q1 2026 Earnings 15.04.</t>
         </is>
       </c>
-      <c r="Q7" s="24" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
+      <c r="Q7" s="39" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R7" s="40">
+        <f>TODAY()-Q7</f>
+        <v/>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
@@ -1130,13 +1142,12 @@
           <t>Q3 FY26 Earnings Jun 2026</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>0</v>
+      <c r="Q8" s="41" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R8" s="42">
+        <f>TODAY()-Q8</f>
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
@@ -1218,13 +1229,12 @@
           <t>29.04.2026 Q3 FY26 Earnings</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="n">
-        <v>0</v>
+      <c r="Q9" s="39" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R9" s="40">
+        <f>TODAY()-Q9</f>
+        <v/>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
@@ -1306,13 +1316,12 @@
           <t>28.05.2026</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R10" s="11" t="n">
-        <v>0</v>
+      <c r="Q10" s="41" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R10" s="42">
+        <f>TODAY()-Q10</f>
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
@@ -1394,13 +1403,12 @@
           <t>H1 2026 Report Juli/Aug 2026</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
+      <c r="Q11" s="39" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R11" s="40">
+        <f>TODAY()-Q11</f>
+        <v/>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
@@ -1482,13 +1490,12 @@
           <t>21.05.2026 Q1 FY27</t>
         </is>
       </c>
-      <c r="Q12" s="25" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R12" s="11" t="n">
-        <v>0</v>
+      <c r="Q12" s="41" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R12" s="42">
+        <f>TODAY()-Q12</f>
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
@@ -1570,13 +1577,12 @@
           <t>07.05.2026</t>
         </is>
       </c>
-      <c r="Q13" s="24" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0</v>
+      <c r="Q13" s="39" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R13" s="40">
+        <f>TODAY()-Q13</f>
+        <v/>
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
@@ -1658,13 +1664,12 @@
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="Q14" s="25" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R14" s="11" t="n">
-        <v>0</v>
+      <c r="Q14" s="41" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R14" s="42">
+        <f>TODAY()-Q14</f>
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1746,13 +1751,12 @@
           <t>22.07.2026</t>
         </is>
       </c>
-      <c r="Q15" s="24" t="inlineStr">
-        <is>
-          <t>18.04.2026</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0</v>
+      <c r="Q15" s="39" t="n">
+        <v>46130</v>
+      </c>
+      <c r="R15" s="40">
+        <f>TODAY()-Q15</f>
+        <v/>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
@@ -1834,13 +1838,12 @@
           <t>23.04.2026 Q1 Earnings</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
-        <is>
-          <t>23.04.2026</t>
-        </is>
-      </c>
-      <c r="R16" s="11" t="n">
-        <v>0</v>
+      <c r="Q16" s="41" t="n">
+        <v>46135</v>
+      </c>
+      <c r="R16" s="42">
+        <f>TODAY()-Q16</f>
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1922,13 +1925,12 @@
           <t>Q2 2025 Earnings 23.07.2025</t>
         </is>
       </c>
-      <c r="Q17" s="24" t="inlineStr">
-        <is>
-          <t>17.04.2026</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0</v>
+      <c r="Q17" s="39" t="n">
+        <v>46129</v>
+      </c>
+      <c r="R17" s="40">
+        <f>TODAY()-Q17</f>
+        <v/>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Satelliten Monitor" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="QuickScreen Ampel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Satelliten Monitor" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QuickScreen Ampel" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="O2" s="31" t="inlineStr">
         <is>
-          <t>Stand: 23.04.2026  |  Broker: Scalable Capital  |  Slots: 11/11</t>
+          <t>Stand: 28.04.2026  |  Broker: Scalable Capital  |  Slots: 11/11</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="H3" s="33" t="inlineStr">
         <is>
-          <t>Eingefroren: MSFT (🔴 FLAG CapEx/OCF, D2) | APH (🔴 FLAG Score-basiert, D2 seit 18.04.) — Sparrate 0€</t>
+          <t>Eingefroren: MSFT (🔴 CapEx/OCF &gt;60%, D2) | APH (🔴 Score-basiert, D2) | AVGO (🔴 Insider-Selling 90d $106M+, ab 27.04.) — Sparrate 0€</t>
         </is>
       </c>
       <c r="K3" s="33" t="inlineStr">
         <is>
-          <t>Ergebnis: 🟢 8 Voll  🟠 1 D2-Sockelbetrag (V)  🔴 2 Eingefroren (MSFT, APH)</t>
+          <t>Ergebnis: 🟢 7 Voll  🟠 1 D2-Sockelbetrag (V)  🔴 3 Eingefroren (MSFT, APH, AVGO)</t>
         </is>
       </c>
       <c r="N3" s="34" t="inlineStr">
@@ -1044,11 +1044,11 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>🟡 DEFCON 3 / ✅ Volle Rate 33,53€ (D3=1.0, Nenner 8.5 post-TMO-Q1)</t>
+          <t>🟡 DEFCON 3 / ✅ Volle Rate 38,00€ (D3=1.0, Nenner 7.5 post-TMO-Q1)</t>
         </is>
       </c>
       <c r="O7" s="8" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
@@ -1131,11 +1131,11 @@
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
-          <t>⚠️ Insider-Check ausstehend (verm. Post-Vesting) | Sparplan läuft</t>
+          <t>🔴 FLAG: Insider-Selling 90d $106M+ (5-14× Schwelle) | OpenInsider 9 Tx „S - Sale" ohne 10b5-1-Suffix | Aktiviert 27.04.2026 | Re-Eval Q3 FY26</t>
         </is>
       </c>
       <c r="O8" s="8" t="n">
-        <v>33.53</v>
+        <v>0</v>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="O10" s="8" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="O11" s="8" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P11" s="5" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="O12" s="8" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="O13" s="8" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="O14" s="8" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>🟠 DEFCON 2 / ⏸ Sockelbetrag 16,76€ | Forward 18.04. nach Advisor-Review | Q2 FY26 28.04.</t>
+          <t>🟠 DEFCON 2 / ⏸ Sockelbetrag 19,00€ | Forward 18.04. nach Advisor-Review | Q2 FY26 28.04.</t>
         </is>
       </c>
       <c r="O15" s="8" t="n">
-        <v>16.76</v>
+        <v>19</v>
       </c>
       <c r="P15" s="5" t="inlineStr">
         <is>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>🟡 DEFCON 3 / ✅ Volle Rate 33,53€ | fcf_trend_neg Resolve (Q1 WC-Unwind) | Q2 ~Ende Juli</t>
+          <t>🟡 DEFCON 3 / ✅ Volle Rate 38,00€ | fcf_trend_neg Resolve (Q1 WC-Unwind) | Q2 ~Ende Juli</t>
         </is>
       </c>
       <c r="O16" s="15" t="n">
-        <v>33.53</v>
+        <v>38</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -833,14 +833,14 @@
       </c>
       <c r="O2" s="31" t="inlineStr">
         <is>
-          <t>Stand: 28.04.2026  |  Broker: Scalable Capital  |  Slots: 11/11</t>
+          <t>Stand: 28.04.2026 spätabends post-V-Rescoring-Revert  |  Broker: Scalable Capital  |  Slots: 11/11</t>
         </is>
       </c>
     </row>
     <row r="3" ht="57.95" customHeight="1" s="30">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Sparrate Satelliten: 285 €/Monat  |  D3/D4-Rate: 33,53€  |  D2-Sockelbetrag: 16,76€ (50%)  |  Nenner 8.5 (v3.7 post-TMO-Q1 23.04.)</t>
+          <t>Sparrate Satelliten: 285 €/Monat  |  D3/D4-Rate: 38,00€  |  D2-Sockelbetrag: 19,00€ (50%)  |  Nenner 7.5 (v3.7 post-AVGO-FLAG-27.04. + V-Rescoring-Revert-28.04. spätabends)</t>
         </is>
       </c>
       <c r="E3" s="33" t="inlineStr">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>63 / DEFCON 2</t>
+          <t>64 / DEFCON 2</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>-23 Backfill-&gt;Forward</t>
+          <t>+1 Codex-Revert vs 28.04. mittags</t>
         </is>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>🟠 DEFCON 2 / ⏸ Sockelbetrag 19,00€ | Forward 18.04. nach Advisor-Review | Q2 FY26 28.04.</t>
+          <t>🟠 DEFCON 2 / ⏸ Sockelbetrag 19,00€ | Q2 Beat-Cascade D3 → Codex-Revert D2 (HIGH-1+2 28.04. spätabends) | Q3 ~Ende Juli ROIC-Verify (PIPELINE #21)</t>
         </is>
       </c>
       <c r="O15" s="8" t="n">
@@ -2051,7 +2051,7 @@
     <row r="24" ht="13.5" customHeight="1" s="30">
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>🔴 EINGEFROREN: MSFT (FLAG CapEx/OCF, D2, Score 59) | APH (FLAG Score-basiert, D2 seit 18.04., Score 63) — Sparrate 0€</t>
+          <t>🔴 EINGEFROREN: MSFT (FLAG CapEx/OCF &gt;60%, D2, Score 59) | APH (FLAG Score-basiert, D2 seit 18.04., Score 63) | AVGO (FLAG Insider-Selling 90d $106M+, D4 Score 84, ab 27.04.) — Sparrate 0€</t>
         </is>
       </c>
       <c r="C24" s="27" t="n"/>
@@ -2075,7 +2075,7 @@
     <row r="25" ht="15" customHeight="1" s="30">
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>🟢 Volle Rate 35,63€ (7 Positionen): ASML/COST/RMS/VEEV/SU/BRK.B D3, AVGO D4  |  🟠 D2-Sockelbetrag 17,81€ (2): V, TMO</t>
+          <t>🟢 Volle Rate 38,00€ (7 Positionen): ASML/COST/RMS/VEEV/SU/BRK.B/TMO D3  |  🟠 D2-Sockelbetrag 19,00€ (1): V  |  🔴 Eingefroren 0€ (3): MSFT, APH, AVGO  |  Nenner 7×1,0 + 1×0,5 + 3×0 = 7,5  |  Σ = 7×38,00 + 1×19,00 + 3×0 = 285,00€ ✓</t>
         </is>
       </c>
       <c r="C25" s="27" t="n"/>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -833,14 +833,14 @@
       </c>
       <c r="O2" s="31" t="inlineStr">
         <is>
-          <t>Stand: 28.04.2026 spätabends post-V-Rescoring-Revert  |  Broker: Scalable Capital  |  Slots: 11/11</t>
+          <t>Stand: 30.04.2026 (APH Q1 FY26 Tag-+1 Vollanalyse Score 63→61)  |  Broker: Scalable Capital  |  Slots: 11/11</t>
         </is>
       </c>
     </row>
     <row r="3" ht="57.95" customHeight="1" s="30">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Sparrate Satelliten: 285 €/Monat  |  D3/D4-Rate: 38,00€  |  D2-Sockelbetrag: 19,00€ (50%)  |  Nenner 7.5 (v3.7 post-AVGO-FLAG-27.04. + V-Rescoring-Revert-28.04. spätabends)</t>
+          <t>Sparrate Satelliten: 285 €/Monat  |  D3/D4-Rate: 38,00€  |  D2-Sockelbetrag: 19,00€ (50%)  |  Nenner 7.5 (v3.7 unverändert post-APH-Score-Move 30.04. — FLAG-Regime stabil)</t>
         </is>
       </c>
       <c r="E3" s="33" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H3" s="33" t="inlineStr">
         <is>
-          <t>Eingefroren: MSFT (🔴 CapEx/OCF &gt;60%, D2) | APH (🔴 Score-basiert, D2) | AVGO (🔴 Insider-Selling 90d $106M+, ab 27.04.) — Sparrate 0€</t>
+          <t>Eingefroren: MSFT (🔴 CapEx/OCF &gt;60%, D2) | APH (🔴 Score-basiert 61, D2) | AVGO (🔴 Insider-Selling 90d $106M+, ab 27.04.) — Sparrate 0€</t>
         </is>
       </c>
       <c r="K3" s="33" t="inlineStr">
@@ -1904,17 +1904,17 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>63 / DEFCON 2</t>
+          <t>61 / DEFCON 2</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>+2 v3.5-&gt;v3.7</t>
+          <t>-2 vs 17.04. (Q1 FY26 Vollanalyse)</t>
         </is>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>🔴 FLAG: Score 63 (DEFCON 2 seit 18.04.) | CN Revenue 14.7% Risk-Map [TC] | Sparrate 0€</t>
+          <t>🔴 FLAG: Score 61 (DEFCON 2, &lt;65 D3-Threshold) | CommScope-NL 1,6x | China-Tax 27% [Q2-Verify ~23.07.] | Sparrate 0€</t>
         </is>
       </c>
       <c r="O17" s="8" t="n">
@@ -2051,7 +2051,7 @@
     <row r="24" ht="13.5" customHeight="1" s="30">
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>🔴 EINGEFROREN: MSFT (FLAG CapEx/OCF &gt;60%, D2, Score 59) | APH (FLAG Score-basiert, D2 seit 18.04., Score 63) | AVGO (FLAG Insider-Selling 90d $106M+, D4 Score 84, ab 27.04.) — Sparrate 0€</t>
+          <t>🔴 EINGEFROREN: MSFT (FLAG CapEx/OCF &gt;60%, D2, Score 59) | APH (FLAG Score-basiert, D2, Score 61 ab 30.04.) | AVGO (FLAG Insider-Selling 90d $106M+, D4 Score 84, ab 27.04.) — Sparrate 0€</t>
         </is>
       </c>
       <c r="C24" s="27" t="n"/>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -1208,17 +1208,17 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>59 / DEFCON 2</t>
+          <t>50 / DEFCON 2</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>-1 v3.5-&gt;v3.7</t>
+          <t>-9 vs 17.04. (Q3 FY26 Tag-+1 V-Q2-Mittelweg)</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>🔴 FLAG: CapEx/OCF &gt;60% | DEFCON 2 (59) | ⏸ Einfrieren</t>
+          <t>🔴 FLAG: CapEx/OCF aktiv (Bull B FAIL CY26 $190B) | DEFCON 2 (50) | ⏸ Einfrieren</t>
         </is>
       </c>
       <c r="O9" s="15" t="n">
@@ -1226,11 +1226,11 @@
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>29.04.2026 Q3 FY26 Earnings</t>
+          <t>Q4 FY26 ~Juli — CapEx-Plateau-Recheck + WACC-Methodology-Verify</t>
         </is>
       </c>
       <c r="Q9" s="39" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="R9" s="40">
         <f>TODAY()-Q9</f>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>[V] Re-Analyse 08.04.: 77-&gt;60 (-17). CapEx/OCF Q2 FY26 83,6% (bereinigt ~63%). ROIC 7,5% &lt; WACC 13,35%. FLAG aktiv. Re-Check 29.04. Q3 FY26 — bereinigtes CapEx/OCF &lt;60% = FLAG-Auflösung möglich.</t>
+          <t>[V] Q3 FY26 Tag-+1 30.04.: Score 59→50, D2/FLAG aktiv unverändert. Triggers A ✅ (CapEx/OCF bereinigt 9M=57,7%) / B ❌ FAIL (CY26 $190B vs Konsens $154,6B Surprise +23%) / C ✅✅ (Azure +39% cc). Quality-Trap aktiv (Wide × Fwd P/E 22,4 max 1; Wide × P/FCF 39,7 hart 0). ROIC 7,68% &lt; WACC 13,64% defeatbeta (Methodology-Watch FRED-Baseline-Verify Q4). Codex-R1+R2-Doppel-Review (V-Q2-Mittelweg via Insider-Skip-Carryover). 4 PIPELINE-Items aktiv (#25-28). Sparrate 0€ unverändert.</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>🟡 ~35–38x</t>
+          <t>🟢 ~22x (Drawdown -25%)</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>🔴 ~7.5%</t>
+          <t>🔴 ~7.7% (defeatbeta-WACC-Methodology-Watch)</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>🔴 FLAG</t>
+          <t>🔴 FLAG (Bull B FAIL)</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>🔴 FLAG / DEFCON 2 / ⏸ EINFRIEREN</t>
+          <t>🔴 FLAG / DEFCON 2 (50) / ⏸ EINFRIEREN</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>Score 59 (↓1 v3.7). DEFCON 2. FLAG CapEx/OCF &gt;60% (bereinigt ~63%). ROIC 7.5% &lt; WACC. Re-Check 29.04.</t>
+          <t>Score 50 (↓9 vs 17.04.). DEFCON 2 unverändert. FLAG CapEx/OCF aktiv (Bull-Case Trigger B FAIL CY26 $190B). Quality-Trap aktiv. Re-Check Q4 FY26 ~Juli.</t>
         </is>
       </c>
     </row>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -1086,27 +1086,27 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>~22x [KB]</t>
+          <t>22.98 [V 30.04.]</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>&gt;20% [KB]</t>
+          <t>3.98% GAAP / 45.7% §410-bereinigt [V 30.04.]</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>~65% [KB]</t>
+          <t>~65% [~]</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>~21% [KB]</t>
+          <t>2.26% Fabless [V 30.04.]</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Wide [KB]</t>
+          <t>Wide / 18 [V 30.04.]</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>84 / DEFCON 4</t>
+          <t>53 / DEFCON 2</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>-2 v3.5-&gt;v3.7</t>
+          <t>Δ-31 30.04. (Quality-Trap)</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
-          <t>🔴 FLAG: Insider-Selling 90d $106M+ (5-14× Schwelle) | OpenInsider 9 Tx „S - Sale" ohne 10b5-1-Suffix | Aktiviert 27.04.2026 | Re-Eval Q3 FY26</t>
+          <t>🔴 FLAG: Insider-Selling 90d $106.4M (5× Schwelle, insider_intel.py 30.04.) | OpenInsider 9 Tx „S - Sale" ohne 10b5-1-Suffix | Aktiviert 27.04.2026 | Vollanalyse 30.04. Score 84→53 (D4→D2) | FLAG aktiv unverändert | Sparrate 0€</t>
         </is>
       </c>
       <c r="O8" s="8" t="n">
@@ -1139,11 +1139,11 @@
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>Q3 FY26 Earnings Jun 2026</t>
+          <t>Q3 FY26 Earnings ~Jun/Jul 2026 (Re-Eval + FLAG-Resolve-Check)</t>
         </is>
       </c>
       <c r="Q8" s="41" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="R8" s="42">
         <f>TODAY()-Q8</f>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>[KB] Kalibrierungsanker 86-&gt;84 (v3.7 Algebra). Fabless CapEx/OCF &lt;15%. AI-Backlog. Insider $123M unter Review — OpenInsider-Check vor FLAG-Aktivierung.</t>
+          <t>[V 30.04.] Forward-Vollanalyse (erste echte seit Skill-Adoption, Pivot von PIPELINE #18 Backfill): Score 84→53 (Δ-31), D4→D2. Quality-Trap voll aktiv (Wide × Fwd P/E 22.98 max 1; Wide × P/FCF 74.4 hart 0). ROIC §410-Goodwill-bereinigt 45.7% (M&amp;A-Compounder VMware/CA/Symantec/Brocade GW 57.2%). FLAG aktiv unverändert (Sparrate 0€, keine Kaskade). Codex R1+R2-Pass 74% Confidence (APPROVE Master-Reading). 5 PIPELINE-Methodology-Watches #30-34.</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>🟢 ~22x</t>
+          <t>🟢 22.98 (max 1 QT)</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>🟢 ~65%</t>
+          <t>🔴 3.98% GAAP (§410: 45.7%)</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>🔴 FLAG</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>🟢 HALTEN</t>
+          <t>🔴 FLAG-Stop</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>Sparplan aktiv. Kalibrierungsanker.</t>
+          <t>Sparplan 0€ (FLAG aktiv 27.04.). Score 53 / D2 nach Vollanalyse 30.04. (Quality-Trap voll aktiv).</t>
         </is>
       </c>
     </row>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="O2" s="31" t="inlineStr">
         <is>
-          <t>Stand: 30.04.2026 (APH Q1 FY26 Tag-+1 Vollanalyse Score 63→61)  |  Broker: Scalable Capital  |  Slots: 11/11</t>
+          <t>Stand: 04.05.2026 abends post-US-Close (BRK.B Q1 FY26 Tag-+1 Vollanalyse + Codex-R1-Korrektur Score 75→71)  |  Broker: Scalable Capital  |  Slots: 11/11</t>
         </is>
       </c>
     </row>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>75 / DEFCON 3</t>
+          <t>71 / DEFCON 3</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>0 v3.5-&gt;v3.7</t>
+          <t>Δ-4 04.05. (Q1 FY26 Tag-+1 Codex-R1-Korrektur)</t>
         </is>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>🟢 Halten | D4→D3 Schema-Alignment 18.04. | Insurance Exception (P/B 1.44x)</t>
+          <t>🟢 Halten | Q1 FY26 Tag-+1 04.05. Score 75→71 D3 unverändert | Insurance Exception (P/B 1.44x)</t>
         </is>
       </c>
       <c r="O14" s="8" t="n">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="Q14" s="41" t="n">
-        <v>46129</v>
+        <v>46146</v>
       </c>
       <c r="R14" s="42">
         <f>TODAY()-Q14</f>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>[~] Insurance Exception: P/B 1,44x. Float $686B, BNSF, 60J Track-Record. Insider: Abel $15,3M Open-Market. CapEx/OCF 45,6% (BNSF+BHE, kein FLAG). D4-&gt;D3 Label-Fix 18.04. Volle Rate 35,63€.</t>
+          <t>[V 04.05.] Q1 FY26 Tag-+1 Vollanalyse Score 75→71 (Codex-R1-Korrektur Δ-4): F=35/M=19/T=1/I=10/S=6. Insurance Exception P/B 1,44x. Float 86B Q1, BNSF/BHE/MSR Operating-Power. Insider Form-4 04.05.: Abel Net Buy 6M $15,3M Open-Market. Cash-ATH effektiv $380,2B (Forbes T-Bill-Settlement bereinigt). 6 Q2-Methodology-Watches PIPELINE #36-#41. Volle Rate 38€.</t>
         </is>
       </c>
     </row>

--- a/03_Tools/Satelliten_Monitor_v2.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v2.0.xlsx
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:S25"/>
+  <dimension ref="A2:S26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="30" min="1" max="1"/>
@@ -833,29 +833,29 @@
       </c>
       <c r="O2" s="31" t="inlineStr">
         <is>
-          <t>Stand: 04.05.2026 abends post-US-Close (BRK.B Q1 FY26 Tag-+1 Vollanalyse + Codex-R1-Korrektur Score 75→71)  |  Broker: Scalable Capital  |  Slots: 11/11</t>
+          <t>Stand: 18.05.2026 (AMZN Neuaufnahme 12. Satellit — Score 42/DEFCON 1, 🔴 CapEx/OCF-FLAG, Sparrate 0€ regelkonform)  |  Broker: Scalable Capital  |  Slots: 12/12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="57.95" customHeight="1" s="30">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Sparrate Satelliten: 285 €/Monat  |  D3/D4-Rate: 38,00€  |  D2-Sockelbetrag: 19,00€ (50%)  |  Nenner 7.5 (v3.7 unverändert post-APH-Score-Move 30.04. — FLAG-Regime stabil)</t>
+          <t>Sparrate Satelliten: 285 €/Monat  |  D3/D4-Rate: 38,00€  |  D2-Sockelbetrag: 19,00€ (50%)  |  Nenner 7.5 (unverändert — AMZN 12. Satellit nenner-neutral, FLAG=Gewicht 0,0; Bestands-11-Raten unberührt)</t>
         </is>
       </c>
       <c r="E3" s="33" t="inlineStr">
         <is>
-          <t>Vollanalysiert: 11 / 11 ✅  |  Geschätzt: 0 / 11</t>
+          <t>Vollanalysiert: 12 / 12 ✅  |  Geschätzt: 0 / 12</t>
         </is>
       </c>
       <c r="H3" s="33" t="inlineStr">
         <is>
-          <t>Eingefroren: MSFT (🔴 CapEx/OCF &gt;60%, D2) | APH (🔴 Score-basiert 61, D2) | AVGO (🔴 Insider-Selling 90d $106M+, ab 27.04.) — Sparrate 0€</t>
+          <t>Eingefroren: MSFT (🔴 CapEx/OCF &gt;60%, D2) | APH (🔴 Score-basiert 61, D2) | AVGO (🔴 Insider-Selling 90d $106M+, ab 27.04.) | AMZN (🔴 CapEx/OCF 99,2%, D1, ab 15.05.) → Sparrate 0€</t>
         </is>
       </c>
       <c r="K3" s="33" t="inlineStr">
         <is>
-          <t>Ergebnis: 🟢 7 Voll  🟠 1 D2-Sockelbetrag (V)  🔴 3 Eingefroren (MSFT, APH, AVGO)</t>
+          <t>Ergebnis: 🟢 7 Voll  🟠 1 D2-Sockelbetrag (V)  🔴 4 Eingefroren (MSFT, APH, AVGO, AMZN)</t>
         </is>
       </c>
       <c r="N3" s="34" t="inlineStr">
@@ -1939,71 +1939,135 @@
       </c>
     </row>
     <row r="18" ht="24.95" customHeight="1" s="30">
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler (AWS/E-Com/Ads)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>2305x [V 15.05.]</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>5.4% GAAP [V 15.05.]</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>~50% [~]</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>~12% [~]</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Wide / 19 [V 15.05.]</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>42 / DEFCON 1</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>NEU 18.05.</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <t>🔴 FLAG: CapEx/OCF 99,2% (TTM netto, &gt;&gt;60%) | DEFCON 1 (42) | Sparrate 0€ | Re-Eval Q2 FY26 ~Juli</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Q2 FY26 ~Ende Juli</t>
+        </is>
+      </c>
+      <c r="Q18" s="39" t="n">
+        <v>46157</v>
+      </c>
+      <c r="R18" s="40">
+        <f>TODAY()-Q18</f>
+        <v/>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>[V 15.05.] Neuaufnahme 12. Satellit (User-Direktive 18.05.). Score 42/D1. CapEx/OCF TTM netto 99,2% (P&amp;E-net $147,3B / OCF $148,5B) &gt;&gt;60%, schaerfer als GOOGL 74-79%. FCF TTM $1,23B -95% YoY. §410 N/A (GW 2,6%). QT-hart fwd_pe/p_fcf 0. ROIC 5,4% GAAP &lt;&lt; WACC 15,57%. Sparrate 0€ regelkonform (kein Owner-Override, FLAG heilig). Resolve-Gate &lt;60%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Sparrate-Check</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="27" t="n"/>
-      <c r="J18" s="27" t="n"/>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="27" t="n"/>
+      <c r="H19" s="27" t="n"/>
+      <c r="I19" s="27" t="n"/>
+      <c r="J19" s="27" t="n"/>
+      <c r="K19" s="27" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="16" t="inlineStr">
         <is>
           <t>Gesamt:</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N19" s="17" t="inlineStr">
         <is>
           <t>→ muss = 285,00 €</t>
         </is>
       </c>
-      <c r="O18" s="18">
-        <f>SUM(O7:O17)</f>
+      <c r="O19" s="18">
+        <f>SUM(O7:O18)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="30">
-      <c r="B20" s="32" t="inlineStr">
+    <row r="20" ht="15.75" customHeight="1" s="30"/>
+    <row r="21" ht="13.5" customHeight="1" s="30">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>LEGENDE &amp; DATENQUALITÄT</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" s="30">
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>✅ Fetched Live – GuruFocus term-pages 02.04.2026: Moat-Scores ASML(9) COST(8) VEEV(8) V(9) MSFT(9)</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="27" t="n"/>
-      <c r="I21" s="27" t="n"/>
-      <c r="J21" s="27" t="n"/>
-      <c r="K21" s="27" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="27" t="n"/>
-      <c r="O21" s="27" t="n"/>
-      <c r="P21" s="27" t="n"/>
-      <c r="Q21" s="27" t="n"/>
-      <c r="R21" s="27" t="n"/>
-      <c r="S21" s="28" t="n"/>
     </row>
     <row r="22" ht="13.5" customHeight="1" s="30">
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>[KB] – Kalibrierungsanalyse: AVGO 86/100 (25.03.), TMO 65→67 (07.04.), ASML 68 (06.04.), MSFT 77→60 (08.04.), APH 61 (09.04.), RMS 71→69 (15.04. Re-Analyse), VEEV 74 (09.04.)</t>
+          <t>✅ Fetched Live – GuruFocus term-pages 02.04.2026: Moat-Scores ASML(9) COST(8) VEEV(8) V(9) MSFT(9)</t>
         </is>
       </c>
       <c r="C22" s="27" t="n"/>
@@ -2027,7 +2091,7 @@
     <row r="23" ht="13.5" customHeight="1" s="30">
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>[~] – Schätzung Wissensbasis (plausibel) | [V] – Vollanalyse verifiziert | [TC] – Tariff-Check abgeschlossen 15.04.2026</t>
+          <t>[KB] – Kalibrierungsanalyse: AVGO 86/100 (25.03.), TMO 65→67 (07.04.), ASML 68 (06.04.), MSFT 77→60 (08.04.), APH 61 (09.04.), RMS 71→69 (15.04. Re-Analyse), VEEV 74 (09.04.)</t>
         </is>
       </c>
       <c r="C23" s="27" t="n"/>
@@ -2051,7 +2115,7 @@
     <row r="24" ht="13.5" customHeight="1" s="30">
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>🔴 EINGEFROREN: MSFT (FLAG CapEx/OCF &gt;60%, D2, Score 59) | APH (FLAG Score-basiert, D2, Score 61 ab 30.04.) | AVGO (FLAG Insider-Selling 90d $106M+, D4 Score 84, ab 27.04.) — Sparrate 0€</t>
+          <t>[~] – Schätzung Wissensbasis (plausibel) | [V] – Vollanalyse verifiziert | [TC] – Tariff-Check abgeschlossen 15.04.2026</t>
         </is>
       </c>
       <c r="C24" s="27" t="n"/>
@@ -2075,7 +2139,7 @@
     <row r="25" ht="15" customHeight="1" s="30">
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>🟢 Volle Rate 38,00€ (7 Positionen): ASML/COST/RMS/VEEV/SU/BRK.B/TMO D3  |  🟠 D2-Sockelbetrag 19,00€ (1): V  |  🔴 Eingefroren 0€ (3): MSFT, APH, AVGO  |  Nenner 7×1,0 + 1×0,5 + 3×0 = 7,5  |  Σ = 7×38,00 + 1×19,00 + 3×0 = 285,00€ ✓</t>
+          <t>🔴 EINGEFROREN: MSFT (FLAG CapEx/OCF &gt;60%, D2, Score 50) | APH (FLAG Score-basiert, D2, Score 61) | AVGO (FLAG Insider-Selling 90d $106M+, D2 Score 53, ab 27.04.) | AMZN (FLAG CapEx/OCF 99,2% TTM, D1 Score 42, Neuaufnahme 12. Satellit ab 15.05.) → Sparrate 0€</t>
         </is>
       </c>
       <c r="C25" s="27" t="n"/>
@@ -2096,24 +2160,48 @@
       <c r="R25" s="27" t="n"/>
       <c r="S25" s="28" t="n"/>
     </row>
+    <row r="26">
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>🟢 Volle Rate 38,00€ (7 Positionen): ASML/COST/RMS/VEEV/SU/BRK.B/TMO D3  |  🟠 D2-Sockelbetrag 19,00€ (1): V  |  🔴 Eingefroren 0€ (4): MSFT, APH, AVGO, AMZN  |  Nenner 7×1,0 + 1×0,5 + 4×0 = 7,5  |  Σ = 7×38,00 + 1×19,00 + 4×0 = 285,00€ ✅</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
+      <c r="H26" s="27" t="n"/>
+      <c r="I26" s="27" t="n"/>
+      <c r="J26" s="27" t="n"/>
+      <c r="K26" s="27" t="n"/>
+      <c r="L26" s="27" t="n"/>
+      <c r="M26" s="27" t="n"/>
+      <c r="N26" s="27" t="n"/>
+      <c r="O26" s="27" t="n"/>
+      <c r="P26" s="27" t="n"/>
+      <c r="Q26" s="27" t="n"/>
+      <c r="R26" s="27" t="n"/>
+      <c r="S26" s="28" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B21:S21"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="B25:S25"/>
     <mergeCell ref="B24:S24"/>
-    <mergeCell ref="B20:S20"/>
+    <mergeCell ref="B19:L19"/>
     <mergeCell ref="B22:S22"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B26:S26"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="B23:S23"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="N3:S3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B18:L18"/>
   </mergeCells>
-  <conditionalFormatting sqref="L7:L17">
+  <conditionalFormatting sqref="L7:L18">
     <cfRule type="expression" priority="16" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("DEFCON 4",L7))</formula>
     </cfRule>
@@ -2127,7 +2215,7 @@
       <formula>ISNUMBER(SEARCH("DEFCON 1",L7))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7:M17">
+  <conditionalFormatting sqref="M7:M18">
     <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2138,7 +2226,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N7:N17">
+  <conditionalFormatting sqref="N7:N18">
     <cfRule type="expression" priority="20" dxfId="10" stopIfTrue="1">
       <formula>LEFT(N7,1)="🔴"</formula>
     </cfRule>
@@ -2161,7 +2249,7 @@
       <formula>ISNUMBER(SEARCH("Halten",N7))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O7:O17">
+  <conditionalFormatting sqref="O7:O18">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>0</formula>
     </cfRule>
@@ -2169,7 +2257,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R7:R17">
+  <conditionalFormatting sqref="R7:R18">
     <cfRule type="cellIs" priority="10" operator="lessThanOrEqual" dxfId="2">
       <formula>30</formula>
     </cfRule>
@@ -2193,7 +2281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I23"/>
+  <dimension ref="A2:I23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="30" min="1" max="1"/>
@@ -2720,6 +2808,48 @@
       <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Score 67 (Q1 FY26 Beat+Raise 23.04.: Adj EPS $5,44 / Rev $11,01B / FCF $825M +121% YoY). D2→D3, Vollrate 33,53€. fcf_trend_neg Resolve (WC-Unwind bestätigt). Q2 ~Ende Juli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>🔴 2305x (QT hart 0)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>🔴 5.4% GAAP (&lt;WACC)</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>🟢 Wide</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>🔴 FLAG</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>🔴 FLAG-Stop</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Score 42 / D1 — Neuaufnahme 12. Satellit 18.05. CapEx/OCF-FLAG TTM 99,2%. Sparrate 0€.</t>
         </is>
       </c>
     </row>
